--- a/project-skills/pipelinecdk/cost-report-generator/assets/template_skeleton.xlsx
+++ b/project-skills/pipelinecdk/cost-report-generator/assets/template_skeleton.xlsx
@@ -13530,7 +13530,7 @@
         <v>8</v>
       </c>
       <c r="AO14" s="8" t="s">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="AP14" s="8">
         <f>SUMIF(Detalle_facturado!AB2:AB100000,AO14,Detalle_facturado!W2:W100000)</f>
